--- a/gu_in/Item.edf/34_RadarItem/RadarItem.xlsx
+++ b/gu_in/Item.edf/34_RadarItem/RadarItem.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48B43326-0E6C-44F5-94B1-8FA527D584FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{540A4FB5-B97F-42C9-822D-888DA749F99A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3315" yWindow="1455" windowWidth="18480" windowHeight="11205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RadarItem" sheetId="1" r:id="rId1"/>
@@ -292,7 +292,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,8 +301,15 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -317,6 +324,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -350,17 +362,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1025,8 +1040,8 @@
       <c r="R3" s="3">
         <v>0</v>
       </c>
-      <c r="S3" s="3">
-        <v>15</v>
+      <c r="S3" s="5">
+        <v>46</v>
       </c>
       <c r="T3" s="3">
         <v>0</v>
@@ -1140,8 +1155,8 @@
       <c r="R4" s="3">
         <v>0</v>
       </c>
-      <c r="S4" s="3">
-        <v>20</v>
+      <c r="S4" s="5">
+        <v>46</v>
       </c>
       <c r="T4" s="3">
         <v>0</v>
@@ -1255,8 +1270,8 @@
       <c r="R5" s="3">
         <v>0</v>
       </c>
-      <c r="S5" s="3">
-        <v>25</v>
+      <c r="S5" s="5">
+        <v>46</v>
       </c>
       <c r="T5" s="3">
         <v>0</v>
@@ -1370,8 +1385,8 @@
       <c r="R6" s="3">
         <v>2</v>
       </c>
-      <c r="S6" s="3">
-        <v>15</v>
+      <c r="S6" s="5">
+        <v>46</v>
       </c>
       <c r="T6" s="3">
         <v>30</v>
@@ -1485,8 +1500,8 @@
       <c r="R7" s="3">
         <v>2</v>
       </c>
-      <c r="S7" s="3">
-        <v>20</v>
+      <c r="S7" s="5">
+        <v>46</v>
       </c>
       <c r="T7" s="3">
         <v>40</v>
@@ -1600,8 +1615,8 @@
       <c r="R8" s="3">
         <v>2</v>
       </c>
-      <c r="S8" s="3">
-        <v>25</v>
+      <c r="S8" s="5">
+        <v>46</v>
       </c>
       <c r="T8" s="3">
         <v>50</v>
@@ -2018,7 +2033,7 @@
       </c>
       <c r="I3">
         <f>RadarItem!S3</f>
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="J3">
         <f>RadarItem!T3</f>
@@ -2168,7 +2183,7 @@
       </c>
       <c r="I4">
         <f>RadarItem!S4</f>
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="J4">
         <f>RadarItem!T4</f>
@@ -2318,7 +2333,7 @@
       </c>
       <c r="I5">
         <f>RadarItem!S5</f>
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="J5">
         <f>RadarItem!T5</f>
@@ -2468,7 +2483,7 @@
       </c>
       <c r="I6">
         <f>RadarItem!S6</f>
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="J6">
         <f>RadarItem!T6</f>
@@ -2618,7 +2633,7 @@
       </c>
       <c r="I7">
         <f>RadarItem!S7</f>
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="J7">
         <f>RadarItem!T7</f>
@@ -2768,7 +2783,7 @@
       </c>
       <c r="I8">
         <f>RadarItem!S8</f>
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="J8">
         <f>RadarItem!T8</f>
